--- a/mode_docx_gen/pmi_gzdzt/part/tsa/GAPC1.xlsx
+++ b/mode_docx_gen/pmi_gzdzt/part/tsa/GAPC1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\www5\mode_docx_gen\pmi_ka\part\tsa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\www5\mode_docx_gen\pmi_lodzt\part\tsa\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="107">
   <si>
     <t>Parameter</t>
   </si>
@@ -145,7 +145,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>ALHGAPCt</t>
+    <t>ALHGAPC_UIRZ</t>
   </si>
   <si>
     <t>SGF2</t>
@@ -232,15 +232,21 @@
     <t>БИ выведены</t>
   </si>
   <si>
-    <t>Превышение времени переключения коммутационного аппарата</t>
-  </si>
-  <si>
-    <t>Прев. вр. пер. КА</t>
-  </si>
-  <si>
     <t>Контр_ОТ_ГЗ</t>
   </si>
   <si>
+    <t>Контр_ОТ_ЗДЗ1</t>
+  </si>
+  <si>
+    <t>Контр_ОТ_ЗДЗ2</t>
+  </si>
+  <si>
+    <t>Контр_ОТ_УРОВ1</t>
+  </si>
+  <si>
+    <t>Контр_ОТ_УРОВ2</t>
+  </si>
+  <si>
     <t>SGF8</t>
   </si>
   <si>
@@ -250,67 +256,55 @@
     <t>SGF10</t>
   </si>
   <si>
+    <t>SGF11</t>
+  </si>
+  <si>
     <t>SGF12</t>
   </si>
   <si>
-    <t>Контр_ОТ_ТН</t>
-  </si>
-  <si>
-    <t>Контр_ОТ_УРОВ</t>
-  </si>
-  <si>
-    <t>Контр_ОТ_ЗДЗ</t>
-  </si>
-  <si>
-    <t>SGF11</t>
-  </si>
-  <si>
     <t>SGF13</t>
   </si>
   <si>
     <t>Контр_ОТ_ТЗ_ТС</t>
   </si>
   <si>
-    <t>Контр_ОТ_сигн_В</t>
-  </si>
-  <si>
-    <t>Контроль опер. тока цепей сигнализации выключателя</t>
+    <t>Контроль положения SA1</t>
+  </si>
+  <si>
+    <t>Контроль положения SA2</t>
+  </si>
+  <si>
+    <t>Контроль положения SA3</t>
+  </si>
+  <si>
+    <t>Контроль положения SA4</t>
+  </si>
+  <si>
+    <t>Контроль положения SG1</t>
+  </si>
+  <si>
+    <t>Контроль положения SG2</t>
+  </si>
+  <si>
+    <t>Контроль положения SG3</t>
+  </si>
+  <si>
+    <t>Контроль опер. тока цепей ГЗ</t>
   </si>
   <si>
     <t>Контроль опер. тока цепей ТЗ, ТС</t>
   </si>
   <si>
-    <t>Контроль опер. тока цепей ГЗ</t>
-  </si>
-  <si>
-    <t>Контроль опер. тока цепей ЗДЗ НН</t>
-  </si>
-  <si>
-    <t>Контроль опер. тока цепей УРОВ НН</t>
-  </si>
-  <si>
-    <t>Контроль опер. тока ИЭУ ТН</t>
-  </si>
-  <si>
-    <t>Контроль положения SA1</t>
-  </si>
-  <si>
-    <t>Контроль положения SA2</t>
-  </si>
-  <si>
-    <t>Контроль положения SA3</t>
-  </si>
-  <si>
-    <t>Контроль положения SA4</t>
-  </si>
-  <si>
-    <t>Контроль положения SA5</t>
-  </si>
-  <si>
-    <t>Контроль положения SG1</t>
-  </si>
-  <si>
-    <t>Контроль положения SG2</t>
+    <t>Контроль опер. тока цепей ЗДЗ НН1</t>
+  </si>
+  <si>
+    <t>Контроль опер. тока цепей ЗДЗ НН2</t>
+  </si>
+  <si>
+    <t>Контроль опер. тока цепей УРОВ НН1</t>
+  </si>
+  <si>
+    <t>Контроль опер. тока цепей УРОВ НН2</t>
   </si>
   <si>
     <t>Контр_полож_SA1</t>
@@ -325,25 +319,25 @@
     <t>Контр_полож_SA4</t>
   </si>
   <si>
-    <t>Контр_полож_SA5</t>
-  </si>
-  <si>
     <t>Контр_полож_SG1</t>
   </si>
   <si>
     <t>Контр_полож_SG2</t>
   </si>
   <si>
+    <t>Контр_полож_SG3</t>
+  </si>
+  <si>
     <t>DescriptionFunc</t>
   </si>
   <si>
+    <t>WeightFunc</t>
+  </si>
+  <si>
+    <t>DZT2_SignAssembly</t>
+  </si>
+  <si>
     <t>Сборка сигналов</t>
-  </si>
-  <si>
-    <t>WeightFunc</t>
-  </si>
-  <si>
-    <t>T_SignAssembly</t>
   </si>
   <si>
     <t>alias</t>
@@ -353,7 +347,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,13 +361,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -421,10 +408,10 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
@@ -455,8 +442,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -763,21 +750,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AE27"/>
+  <dimension ref="A1:AE26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="48.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="46" style="3" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.5703125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="4.42578125" style="5" customWidth="1"/>
-    <col min="11" max="11" width="4.5703125" style="5" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="5" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" style="3" customWidth="1"/>
+    <col min="9" max="12" width="9.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="19" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="26" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="27" max="30" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
@@ -875,7 +859,7 @@
         <v>34</v>
       </c>
       <c r="AE1" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -1984,22 +1968,22 @@
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>71</v>
+      <c r="C14" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>39</v>
@@ -2007,17 +1991,17 @@
       <c r="H14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>40</v>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>41</v>
@@ -2044,22 +2028,22 @@
         <v>0</v>
       </c>
       <c r="U14" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="6">
         <v>0</v>
       </c>
       <c r="W14" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>40</v>
@@ -2082,13 +2066,13 @@
         <v>36</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>38</v>
@@ -2174,13 +2158,13 @@
         <v>36</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>38</v>
@@ -2266,13 +2250,13 @@
         <v>36</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>38</v>
@@ -2358,13 +2342,13 @@
         <v>36</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>38</v>
@@ -2450,13 +2434,13 @@
         <v>36</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>38</v>
@@ -2542,13 +2526,13 @@
         <v>36</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>38</v>
@@ -2626,95 +2610,95 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>103</v>
+        <v>89</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I21" s="5">
-        <v>0</v>
-      </c>
-      <c r="J21" s="5">
-        <v>1</v>
-      </c>
-      <c r="K21" s="5">
-        <v>1</v>
-      </c>
-      <c r="L21" s="5">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="s">
+      <c r="H21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8">
+        <v>1</v>
+      </c>
+      <c r="K21" s="8">
+        <v>1</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="T21" s="6">
-        <v>0</v>
-      </c>
-      <c r="U21" s="6">
-        <v>0</v>
-      </c>
-      <c r="V21" s="6">
-        <v>0</v>
-      </c>
-      <c r="W21" s="6">
-        <v>0</v>
-      </c>
-      <c r="X21" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD21" s="3" t="s">
+      <c r="N21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T21" s="9">
+        <v>0</v>
+      </c>
+      <c r="U21" s="9">
+        <v>0</v>
+      </c>
+      <c r="V21" s="9">
+        <v>0</v>
+      </c>
+      <c r="W21" s="9">
+        <v>0</v>
+      </c>
+      <c r="X21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD21" s="7" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2726,13 +2710,13 @@
         <v>36</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>72</v>
+        <v>90</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>38</v>
@@ -2755,7 +2739,7 @@
       <c r="L22" s="8">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="M22" s="7" t="s">
         <v>41</v>
       </c>
       <c r="N22" s="7" t="s">
@@ -2818,13 +2802,13 @@
         <v>36</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>82</v>
+        <v>91</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>38</v>
@@ -2847,7 +2831,7 @@
       <c r="L23" s="8">
         <v>0</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="M23" s="7" t="s">
         <v>41</v>
       </c>
       <c r="N23" s="7" t="s">
@@ -2910,13 +2894,13 @@
         <v>36</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>83</v>
+        <v>92</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>38</v>
@@ -2939,7 +2923,7 @@
       <c r="L24" s="8">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="M24" s="7" t="s">
         <v>41</v>
       </c>
       <c r="N24" s="7" t="s">
@@ -3002,13 +2986,13 @@
         <v>36</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>38</v>
@@ -3031,7 +3015,7 @@
       <c r="L25" s="8">
         <v>0</v>
       </c>
-      <c r="M25" s="3" t="s">
+      <c r="M25" s="7" t="s">
         <v>41</v>
       </c>
       <c r="N25" s="7" t="s">
@@ -3094,13 +3078,13 @@
         <v>36</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>38</v>
@@ -3123,7 +3107,7 @@
       <c r="L26" s="8">
         <v>0</v>
       </c>
-      <c r="M26" s="3" t="s">
+      <c r="M26" s="7" t="s">
         <v>41</v>
       </c>
       <c r="N26" s="7" t="s">
@@ -3175,98 +3159,6 @@
         <v>40</v>
       </c>
       <c r="AD26" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I27" s="8">
-        <v>0</v>
-      </c>
-      <c r="J27" s="8">
-        <v>1</v>
-      </c>
-      <c r="K27" s="8">
-        <v>1</v>
-      </c>
-      <c r="L27" s="8">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="S27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T27" s="9">
-        <v>0</v>
-      </c>
-      <c r="U27" s="9">
-        <v>0</v>
-      </c>
-      <c r="V27" s="9">
-        <v>0</v>
-      </c>
-      <c r="W27" s="9">
-        <v>0</v>
-      </c>
-      <c r="X27" s="9">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="9">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD27" s="7" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3283,8 +3175,8 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3299,7 +3191,7 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3308,7 +3200,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3319,7 +3211,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s">
         <v>105</v>
@@ -3327,7 +3219,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B6">
         <v>10</v>
